--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,6 +1793,327 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125939339</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104245</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelört</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thesium alpinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Möllaremossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>551874</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6341947</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Christian Bertelsen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Christian Bertelsen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125939195</v>
+      </c>
+      <c r="B13" t="n">
+        <v>108932</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Möllaremossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>551874</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6341947</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Christian Bertelsen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Christian Bertelsen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125939380</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100513</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Möllaremossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>551874</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6341947</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Christian Bertelsen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Christian Bertelsen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>104245</v>
+        <v>108932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>108932</v>
+        <v>104245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>108932</v>
+        <v>108933</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>104245</v>
+        <v>104246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100513</v>
+        <v>100514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>108933</v>
+        <v>104248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>104246</v>
+        <v>108935</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100514</v>
+        <v>100516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>104248</v>
+        <v>104252</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>108935</v>
+        <v>108939</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>104252</v>
+        <v>104253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>108939</v>
+        <v>108940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>104253</v>
+        <v>108942</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>108940</v>
+        <v>104255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>108942</v>
+        <v>108944</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>104255</v>
+        <v>104257</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>108944</v>
+        <v>104257</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>104257</v>
+        <v>108944</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>104257</v>
+        <v>108948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>108944</v>
+        <v>104261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>108948</v>
+        <v>104274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>104261</v>
+        <v>108961</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>104274</v>
+        <v>108961</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>108961</v>
+        <v>104274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>108961</v>
+        <v>108964</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>104274</v>
+        <v>104277</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>108964</v>
+        <v>104277</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>104277</v>
+        <v>108964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>104277</v>
+        <v>104286</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>108964</v>
+        <v>108973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>125939380</v>
       </c>
       <c r="B14" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B12" t="n">
-        <v>104286</v>
+        <v>108973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B13" t="n">
-        <v>108973</v>
+        <v>104286</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60252-2022 artfynd.xlsx
+++ b/artfynd/A 60252-2022 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939195</v>
+        <v>125939339</v>
       </c>
       <c r="B12" t="n">
-        <v>108973</v>
+        <v>104286</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220228</v>
+        <v>1560</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939339</v>
+        <v>125939195</v>
       </c>
       <c r="B13" t="n">
-        <v>104286</v>
+        <v>108973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1560</v>
+        <v>220228</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
